--- a/usd_krw_6m.xlsx
+++ b/usd_krw_6m.xlsx
@@ -25,9 +25,6 @@
     <t>02:00 종가</t>
   </si>
   <si>
-    <t>2025-11-21</t>
-  </si>
-  <si>
     <t>2025-11-24</t>
   </si>
   <si>
@@ -383,6 +380,9 @@
   </si>
   <si>
     <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
   </si>
 </sst>
 </file>
@@ -560,364 +560,364 @@
               <c:strCache>
                 <c:ptCount val="120"/>
                 <c:pt idx="0">
-                  <c:v>2025-11-21</c:v>
+                  <c:v>2025-11-24</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2025-11-24</c:v>
+                  <c:v>2025-11-25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2025-11-25</c:v>
+                  <c:v>2025-11-26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2025-11-26</c:v>
+                  <c:v>2025-11-27</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2025-11-27</c:v>
+                  <c:v>2025-11-28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2025-11-28</c:v>
+                  <c:v>2025-12-01</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2025-12-01</c:v>
+                  <c:v>2025-12-02</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2025-12-02</c:v>
+                  <c:v>2025-12-03</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2025-12-03</c:v>
+                  <c:v>2025-12-04</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2025-12-04</c:v>
+                  <c:v>2025-12-05</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2025-12-05</c:v>
+                  <c:v>2025-12-08</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2025-12-08</c:v>
+                  <c:v>2025-12-09</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2025-12-09</c:v>
+                  <c:v>2025-12-10</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2025-12-10</c:v>
+                  <c:v>2025-12-11</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2025-12-11</c:v>
+                  <c:v>2025-12-12</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2025-12-12</c:v>
+                  <c:v>2025-12-15</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2025-12-15</c:v>
+                  <c:v>2025-12-16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2025-12-16</c:v>
+                  <c:v>2025-12-17</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2025-12-17</c:v>
+                  <c:v>2025-12-18</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2025-12-18</c:v>
+                  <c:v>2025-12-19</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2025-12-19</c:v>
+                  <c:v>2025-12-22</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2025-12-22</c:v>
+                  <c:v>2025-12-23</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2025-12-23</c:v>
+                  <c:v>2025-12-24</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2025-12-24</c:v>
+                  <c:v>2025-12-26</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2025-12-26</c:v>
+                  <c:v>2025-12-29</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2025-12-29</c:v>
+                  <c:v>2025-12-30</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2025-12-30</c:v>
+                  <c:v>2026-01-02</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2026-01-02</c:v>
+                  <c:v>2026-01-05</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2026-01-05</c:v>
+                  <c:v>2026-01-06</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2026-01-06</c:v>
+                  <c:v>2026-01-07</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2026-01-07</c:v>
+                  <c:v>2026-01-08</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2026-01-08</c:v>
+                  <c:v>2026-01-09</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2026-01-09</c:v>
+                  <c:v>2026-01-12</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2026-01-12</c:v>
+                  <c:v>2026-01-13</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2026-01-13</c:v>
+                  <c:v>2026-01-14</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2026-01-14</c:v>
+                  <c:v>2026-01-15</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2026-01-15</c:v>
+                  <c:v>2026-01-16</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2026-01-16</c:v>
+                  <c:v>2026-01-19</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2026-01-19</c:v>
+                  <c:v>2026-01-20</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2026-01-20</c:v>
+                  <c:v>2026-01-21</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2026-01-21</c:v>
+                  <c:v>2026-01-22</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2026-01-22</c:v>
+                  <c:v>2026-01-23</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2026-01-23</c:v>
+                  <c:v>2026-01-26</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2026-01-26</c:v>
+                  <c:v>2026-01-27</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2026-01-27</c:v>
+                  <c:v>2026-01-28</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2026-01-28</c:v>
+                  <c:v>2026-01-29</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2026-01-29</c:v>
+                  <c:v>2026-01-30</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2026-01-30</c:v>
+                  <c:v>2026-02-02</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2026-02-02</c:v>
+                  <c:v>2026-02-03</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2026-02-03</c:v>
+                  <c:v>2026-02-04</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2026-02-04</c:v>
+                  <c:v>2026-02-05</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2026-02-05</c:v>
+                  <c:v>2026-02-06</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2026-02-06</c:v>
+                  <c:v>2026-02-09</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2026-02-09</c:v>
+                  <c:v>2026-02-10</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2026-02-10</c:v>
+                  <c:v>2026-02-11</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2026-02-11</c:v>
+                  <c:v>2026-02-12</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2026-02-12</c:v>
+                  <c:v>2026-02-13</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2026-02-13</c:v>
+                  <c:v>2026-02-19</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2026-02-19</c:v>
+                  <c:v>2026-02-20</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2026-02-20</c:v>
+                  <c:v>2026-02-23</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>2026-02-23</c:v>
+                  <c:v>2026-02-24</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2026-02-24</c:v>
+                  <c:v>2026-02-25</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>2026-02-25</c:v>
+                  <c:v>2026-02-26</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>2026-02-26</c:v>
+                  <c:v>2026-02-27</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>2026-02-27</c:v>
+                  <c:v>2026-03-03</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>2026-03-03</c:v>
+                  <c:v>2026-03-04</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>2026-03-04</c:v>
+                  <c:v>2026-03-05</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>2026-03-05</c:v>
+                  <c:v>2026-03-06</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>2026-03-06</c:v>
+                  <c:v>2026-03-09</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>2026-03-09</c:v>
+                  <c:v>2026-03-10</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>2026-03-10</c:v>
+                  <c:v>2026-03-11</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2026-03-11</c:v>
+                  <c:v>2026-03-12</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>2026-03-12</c:v>
+                  <c:v>2026-03-13</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>2026-03-13</c:v>
+                  <c:v>2026-03-16</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>2026-03-16</c:v>
+                  <c:v>2026-03-17</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>2026-03-17</c:v>
+                  <c:v>2026-03-18</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>2026-03-18</c:v>
+                  <c:v>2026-03-19</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>2026-03-19</c:v>
+                  <c:v>2026-03-20</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>2026-03-20</c:v>
+                  <c:v>2026-03-23</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>2026-03-23</c:v>
+                  <c:v>2026-03-24</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>2026-03-24</c:v>
+                  <c:v>2026-03-25</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>2026-03-25</c:v>
+                  <c:v>2026-03-26</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>2026-03-26</c:v>
+                  <c:v>2026-03-27</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>2026-03-27</c:v>
+                  <c:v>2026-03-30</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2026-03-30</c:v>
+                  <c:v>2026-03-31</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>2026-03-31</c:v>
+                  <c:v>2026-04-01</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>2026-04-01</c:v>
+                  <c:v>2026-04-02</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2026-04-02</c:v>
+                  <c:v>2026-04-03</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>2026-04-03</c:v>
+                  <c:v>2026-04-06</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>2026-04-06</c:v>
+                  <c:v>2026-04-07</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>2026-04-07</c:v>
+                  <c:v>2026-04-08</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>2026-04-08</c:v>
+                  <c:v>2026-04-09</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>2026-04-09</c:v>
+                  <c:v>2026-04-10</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>2026-04-10</c:v>
+                  <c:v>2026-04-13</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>2026-04-13</c:v>
+                  <c:v>2026-04-14</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>2026-04-14</c:v>
+                  <c:v>2026-04-15</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>2026-04-15</c:v>
+                  <c:v>2026-04-16</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>2026-04-16</c:v>
+                  <c:v>2026-04-17</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>2026-04-17</c:v>
+                  <c:v>2026-04-20</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>2026-04-20</c:v>
+                  <c:v>2026-04-21</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>2026-04-21</c:v>
+                  <c:v>2026-04-22</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>2026-04-22</c:v>
+                  <c:v>2026-04-23</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>2026-04-23</c:v>
+                  <c:v>2026-04-24</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>2026-04-24</c:v>
+                  <c:v>2026-04-27</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>2026-04-27</c:v>
+                  <c:v>2026-04-28</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>2026-04-28</c:v>
+                  <c:v>2026-04-29</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>2026-04-29</c:v>
+                  <c:v>2026-04-30</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>2026-04-30</c:v>
+                  <c:v>2026-05-04</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>2026-05-04</c:v>
+                  <c:v>2026-05-06</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>2026-05-06</c:v>
+                  <c:v>2026-05-07</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>2026-05-07</c:v>
+                  <c:v>2026-05-08</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>2026-05-08</c:v>
+                  <c:v>2026-05-11</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>2026-05-11</c:v>
+                  <c:v>2026-05-12</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>2026-05-12</c:v>
+                  <c:v>2026-05-13</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>2026-05-13</c:v>
+                  <c:v>2026-05-14</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>2026-05-14</c:v>
+                  <c:v>2026-05-15</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>2026-05-15</c:v>
+                  <c:v>2026-05-18</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>2026-05-18</c:v>
+                  <c:v>2026-05-19</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>2026-05-19</c:v>
+                  <c:v>2026-05-20</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>2026-05-20</c:v>
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -929,364 +929,364 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="120"/>
                 <c:pt idx="0">
-                  <c:v>1475.6</c:v>
+                  <c:v>1477.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1477.1</c:v>
+                  <c:v>1472.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1472.4</c:v>
+                  <c:v>1465.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1465.6</c:v>
+                  <c:v>1464.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1464.9</c:v>
+                  <c:v>1470.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1469.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1468.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1468</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1473.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1468.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1466.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1472.3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1470.4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1473</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1473.7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1471</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1477</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1479.8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1478.3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1476.3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1480.1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1483.6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1449.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1440.3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1429.8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1439</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1441.8</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1443.8</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1445.4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1445.8</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1450.6</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1457.6</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1468.4</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1473.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1477.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1469.7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1473.6</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1473.7</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1478.1</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1471.3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1469.9</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1465.8</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1440.6</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1446.2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1422.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1426.3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1439.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1464.3</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1445.4</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1450.2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1469</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1469.5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1460.3</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1459.1</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1450.1</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1440.2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1444.9</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1445.5</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1446.6</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1440</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1442.5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1429.4</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1425.8</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1439.7</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1466.1</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1476.2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1468.1</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1476.4</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1495.5</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1469.2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1466.5</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1481.2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1493.7</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1497.5</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1493.6</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1483.1</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1501</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1500.6</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>1517.3</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1495.2</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1499.7</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1507</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1508.9</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1515.7</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>1530.1</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1501.3</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1519.7</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>1505.2</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1506.3</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1504.2</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>1470.6</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>1469.9</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1468.4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1468</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1473.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1468.8</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1466.9</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1472.3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1470.4</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1473</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1473.7</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1471</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1477</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1479.8</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1478.3</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1476.3</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1480.1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1483.6</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1449.8</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1440.3</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1429.8</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1439</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1441.8</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1443.8</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1445.4</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1445.8</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1450.6</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1457.6</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1468.4</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1473.7</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1477.5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1469.7</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1473.6</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1473.7</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1478.1</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1471.3</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1469.9</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1465.8</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1440.6</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1446.2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1422.5</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1426.3</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1439.5</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>1464.3</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1445.4</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1450.2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1469</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1469.5</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1460.3</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1459.1</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1450.1</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1440.2</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1444.9</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1445.5</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1446.6</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>1440</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1442.5</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>1429.4</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>1425.8</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>1439.7</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>1466.1</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>1476.2</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>1468.1</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>1476.4</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>1495.5</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>1469.2</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>1466.5</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>1481.2</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>1493.7</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>1497.5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>1493.6</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>1483.1</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>1501</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>1500.6</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>1517.3</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>1495.2</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1499.7</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>1507</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>1508.9</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>1515.7</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>1530.1</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>1501.3</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>1519.7</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>1505.2</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>1506.3</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>1504.2</c:v>
-                </c:pt>
                 <c:pt idx="91">
-                  <c:v>1470.6</c:v>
+                  <c:v>1482.5</c:v>
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>1482.5</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>1482.5</c:v>
+                  <c:v>1489.3</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>1489.3</c:v>
+                  <c:v>1481.2</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>1481.2</c:v>
+                  <c:v>1474.2</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>1474.2</c:v>
+                  <c:v>1474.6</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>1474.6</c:v>
+                  <c:v>1483.5</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>1483.5</c:v>
+                  <c:v>1477.2</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>1477.2</c:v>
+                  <c:v>1468.5</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>1468.5</c:v>
+                  <c:v>1476</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>1476</c:v>
+                  <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>1481</c:v>
+                  <c:v>1484.5</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>1484.5</c:v>
+                  <c:v>1472.5</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>1472.5</c:v>
+                  <c:v>1473.6</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>1473.6</c:v>
+                  <c:v>1479</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>1479</c:v>
+                  <c:v>1483.3</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>1483.3</c:v>
+                  <c:v>1462.8</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>1462.8</c:v>
+                  <c:v>1455.1</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>1455.1</c:v>
+                  <c:v>1454</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>1454</c:v>
+                  <c:v>1471.7</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>1471.7</c:v>
+                  <c:v>1472.4</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>1472.4</c:v>
+                  <c:v>1489.9</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>1489.9</c:v>
+                  <c:v>1490.6</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>1490.6</c:v>
+                  <c:v>1491</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>1491</c:v>
+                  <c:v>1500.8</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>1500.8</c:v>
+                  <c:v>1500.3</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>1500.3</c:v>
+                  <c:v>1507.8</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>1507.8</c:v>
+                  <c:v>1506.8</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>1506.8</c:v>
+                  <c:v>1506.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1431,364 +1431,364 @@
               <c:strCache>
                 <c:ptCount val="120"/>
                 <c:pt idx="0">
-                  <c:v>2025-11-21</c:v>
+                  <c:v>2025-11-24</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2025-11-24</c:v>
+                  <c:v>2025-11-25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2025-11-25</c:v>
+                  <c:v>2025-11-26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2025-11-26</c:v>
+                  <c:v>2025-11-27</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2025-11-27</c:v>
+                  <c:v>2025-11-28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2025-11-28</c:v>
+                  <c:v>2025-12-01</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2025-12-01</c:v>
+                  <c:v>2025-12-02</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2025-12-02</c:v>
+                  <c:v>2025-12-03</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2025-12-03</c:v>
+                  <c:v>2025-12-04</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2025-12-04</c:v>
+                  <c:v>2025-12-05</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2025-12-05</c:v>
+                  <c:v>2025-12-08</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2025-12-08</c:v>
+                  <c:v>2025-12-09</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2025-12-09</c:v>
+                  <c:v>2025-12-10</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2025-12-10</c:v>
+                  <c:v>2025-12-11</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2025-12-11</c:v>
+                  <c:v>2025-12-12</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2025-12-12</c:v>
+                  <c:v>2025-12-15</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2025-12-15</c:v>
+                  <c:v>2025-12-16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2025-12-16</c:v>
+                  <c:v>2025-12-17</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2025-12-17</c:v>
+                  <c:v>2025-12-18</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2025-12-18</c:v>
+                  <c:v>2025-12-19</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2025-12-19</c:v>
+                  <c:v>2025-12-22</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2025-12-22</c:v>
+                  <c:v>2025-12-23</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2025-12-23</c:v>
+                  <c:v>2025-12-24</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2025-12-24</c:v>
+                  <c:v>2025-12-26</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2025-12-26</c:v>
+                  <c:v>2025-12-29</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2025-12-29</c:v>
+                  <c:v>2025-12-30</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2025-12-30</c:v>
+                  <c:v>2026-01-02</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2026-01-02</c:v>
+                  <c:v>2026-01-05</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2026-01-05</c:v>
+                  <c:v>2026-01-06</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2026-01-06</c:v>
+                  <c:v>2026-01-07</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2026-01-07</c:v>
+                  <c:v>2026-01-08</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2026-01-08</c:v>
+                  <c:v>2026-01-09</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2026-01-09</c:v>
+                  <c:v>2026-01-12</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2026-01-12</c:v>
+                  <c:v>2026-01-13</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2026-01-13</c:v>
+                  <c:v>2026-01-14</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2026-01-14</c:v>
+                  <c:v>2026-01-15</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2026-01-15</c:v>
+                  <c:v>2026-01-16</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2026-01-16</c:v>
+                  <c:v>2026-01-19</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2026-01-19</c:v>
+                  <c:v>2026-01-20</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2026-01-20</c:v>
+                  <c:v>2026-01-21</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2026-01-21</c:v>
+                  <c:v>2026-01-22</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2026-01-22</c:v>
+                  <c:v>2026-01-23</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2026-01-23</c:v>
+                  <c:v>2026-01-26</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2026-01-26</c:v>
+                  <c:v>2026-01-27</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2026-01-27</c:v>
+                  <c:v>2026-01-28</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2026-01-28</c:v>
+                  <c:v>2026-01-29</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2026-01-29</c:v>
+                  <c:v>2026-01-30</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2026-01-30</c:v>
+                  <c:v>2026-02-02</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2026-02-02</c:v>
+                  <c:v>2026-02-03</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2026-02-03</c:v>
+                  <c:v>2026-02-04</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2026-02-04</c:v>
+                  <c:v>2026-02-05</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2026-02-05</c:v>
+                  <c:v>2026-02-06</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2026-02-06</c:v>
+                  <c:v>2026-02-09</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2026-02-09</c:v>
+                  <c:v>2026-02-10</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2026-02-10</c:v>
+                  <c:v>2026-02-11</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2026-02-11</c:v>
+                  <c:v>2026-02-12</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2026-02-12</c:v>
+                  <c:v>2026-02-13</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2026-02-13</c:v>
+                  <c:v>2026-02-19</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2026-02-19</c:v>
+                  <c:v>2026-02-20</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2026-02-20</c:v>
+                  <c:v>2026-02-23</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>2026-02-23</c:v>
+                  <c:v>2026-02-24</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2026-02-24</c:v>
+                  <c:v>2026-02-25</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>2026-02-25</c:v>
+                  <c:v>2026-02-26</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>2026-02-26</c:v>
+                  <c:v>2026-02-27</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>2026-02-27</c:v>
+                  <c:v>2026-03-03</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>2026-03-03</c:v>
+                  <c:v>2026-03-04</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>2026-03-04</c:v>
+                  <c:v>2026-03-05</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>2026-03-05</c:v>
+                  <c:v>2026-03-06</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>2026-03-06</c:v>
+                  <c:v>2026-03-09</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>2026-03-09</c:v>
+                  <c:v>2026-03-10</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>2026-03-10</c:v>
+                  <c:v>2026-03-11</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2026-03-11</c:v>
+                  <c:v>2026-03-12</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>2026-03-12</c:v>
+                  <c:v>2026-03-13</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>2026-03-13</c:v>
+                  <c:v>2026-03-16</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>2026-03-16</c:v>
+                  <c:v>2026-03-17</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>2026-03-17</c:v>
+                  <c:v>2026-03-18</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>2026-03-18</c:v>
+                  <c:v>2026-03-19</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>2026-03-19</c:v>
+                  <c:v>2026-03-20</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>2026-03-20</c:v>
+                  <c:v>2026-03-23</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>2026-03-23</c:v>
+                  <c:v>2026-03-24</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>2026-03-24</c:v>
+                  <c:v>2026-03-25</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>2026-03-25</c:v>
+                  <c:v>2026-03-26</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>2026-03-26</c:v>
+                  <c:v>2026-03-27</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>2026-03-27</c:v>
+                  <c:v>2026-03-30</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2026-03-30</c:v>
+                  <c:v>2026-03-31</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>2026-03-31</c:v>
+                  <c:v>2026-04-01</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>2026-04-01</c:v>
+                  <c:v>2026-04-02</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2026-04-02</c:v>
+                  <c:v>2026-04-03</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>2026-04-03</c:v>
+                  <c:v>2026-04-06</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>2026-04-06</c:v>
+                  <c:v>2026-04-07</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>2026-04-07</c:v>
+                  <c:v>2026-04-08</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>2026-04-08</c:v>
+                  <c:v>2026-04-09</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>2026-04-09</c:v>
+                  <c:v>2026-04-10</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>2026-04-10</c:v>
+                  <c:v>2026-04-13</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>2026-04-13</c:v>
+                  <c:v>2026-04-14</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>2026-04-14</c:v>
+                  <c:v>2026-04-15</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>2026-04-15</c:v>
+                  <c:v>2026-04-16</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>2026-04-16</c:v>
+                  <c:v>2026-04-17</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>2026-04-17</c:v>
+                  <c:v>2026-04-20</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>2026-04-20</c:v>
+                  <c:v>2026-04-21</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>2026-04-21</c:v>
+                  <c:v>2026-04-22</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>2026-04-22</c:v>
+                  <c:v>2026-04-23</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>2026-04-23</c:v>
+                  <c:v>2026-04-24</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>2026-04-24</c:v>
+                  <c:v>2026-04-27</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>2026-04-27</c:v>
+                  <c:v>2026-04-28</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>2026-04-28</c:v>
+                  <c:v>2026-04-29</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>2026-04-29</c:v>
+                  <c:v>2026-04-30</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>2026-04-30</c:v>
+                  <c:v>2026-05-04</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>2026-05-04</c:v>
+                  <c:v>2026-05-06</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>2026-05-06</c:v>
+                  <c:v>2026-05-07</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>2026-05-07</c:v>
+                  <c:v>2026-05-08</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>2026-05-08</c:v>
+                  <c:v>2026-05-11</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>2026-05-11</c:v>
+                  <c:v>2026-05-12</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>2026-05-12</c:v>
+                  <c:v>2026-05-13</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>2026-05-13</c:v>
+                  <c:v>2026-05-14</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>2026-05-14</c:v>
+                  <c:v>2026-05-15</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>2026-05-15</c:v>
+                  <c:v>2026-05-18</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>2026-05-18</c:v>
+                  <c:v>2026-05-19</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>2026-05-19</c:v>
+                  <c:v>2026-05-20</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>2026-05-20</c:v>
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1800,364 +1800,364 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="120"/>
                 <c:pt idx="0">
-                  <c:v>1471.5</c:v>
+                  <c:v>1476.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1476.5</c:v>
+                  <c:v>1469.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1469.3</c:v>
+                  <c:v>1468.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1468.3</c:v>
+                  <c:v>1462.7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1462.7</c:v>
+                  <c:v>1466.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1466.8</c:v>
+                  <c:v>1468</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1468</c:v>
+                  <c:v>1469.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1469.4</c:v>
+                  <c:v>1466.9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1466.9</c:v>
+                  <c:v>1473.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1473.6</c:v>
+                  <c:v>1473.3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1473.3</c:v>
+                  <c:v>1469.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1469.8</c:v>
+                  <c:v>1469.9</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1469.9</c:v>
+                  <c:v>1470.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1470.8</c:v>
+                  <c:v>1471.9</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1471.9</c:v>
+                  <c:v>1477</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1477</c:v>
+                  <c:v>1468.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1468.6</c:v>
+                  <c:v>1473</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1473</c:v>
+                  <c:v>1474.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1474.5</c:v>
+                  <c:v>1473.1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1473.1</c:v>
+                  <c:v>1478</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1478</c:v>
+                  <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1481</c:v>
+                  <c:v>1445.7</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1445.7</c:v>
+                  <c:v>1442.2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1442.2</c:v>
+                  <c:v>1434.1</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1434.1</c:v>
+                  <c:v>1439.5</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1439.5</c:v>
+                  <c:v>1444.7</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1444.7</c:v>
+                  <c:v>1445.6</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1445.6</c:v>
+                  <c:v>1447.1</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1447.1</c:v>
+                  <c:v>1447.6</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1447.6</c:v>
+                  <c:v>1451.8</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1451.8</c:v>
+                  <c:v>1459</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1459</c:v>
+                  <c:v>1468.8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1468.8</c:v>
+                  <c:v>1478.8</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1478.8</c:v>
+                  <c:v>1464</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1464</c:v>
+                  <c:v>1469.2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1469.2</c:v>
+                  <c:v>1474.5</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1474.5</c:v>
+                  <c:v>1473.1</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1473.1</c:v>
+                  <c:v>1476.7</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1476.7</c:v>
+                  <c:v>1465.9</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1465.9</c:v>
+                  <c:v>1464.5</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1464.5</c:v>
+                  <c:v>1462.5</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1462.5</c:v>
+                  <c:v>1443.9</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1443.9</c:v>
+                  <c:v>1437.5</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1437.5</c:v>
+                  <c:v>1436.1</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1436.1</c:v>
+                  <c:v>1434</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1434</c:v>
+                  <c:v>1443.5</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1443.5</c:v>
+                  <c:v>1451.5</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1451.5</c:v>
+                  <c:v>1446.6</c:v>
                 </c:pt>
                 <c:pt idx="49">
+                  <c:v>1459.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1463.7</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1463</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1457.7</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1457.2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1447</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1438.6</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1444.6</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1448.9</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1446.6</c:v>
                 </c:pt>
-                <c:pt idx="50">
-                  <c:v>1459.5</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1463.7</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1463</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1457.7</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1457.2</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1447</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1438.6</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1444.6</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1448.9</c:v>
-                </c:pt>
                 <c:pt idx="59">
-                  <c:v>1446.6</c:v>
+                  <c:v>1442.9</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1442.9</c:v>
+                  <c:v>1441</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1441</c:v>
+                  <c:v>1427.8</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>1427.8</c:v>
+                  <c:v>1433.5</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>1433.5</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>1440</c:v>
+                  <c:v>1485.7</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>1485.7</c:v>
+                  <c:v>1462.9</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1462.9</c:v>
+                  <c:v>1482.2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1482.2</c:v>
+                  <c:v>1481.6</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1481.6</c:v>
+                  <c:v>1473.7</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1473.7</c:v>
+                  <c:v>1465.7</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1465.7</c:v>
+                  <c:v>1477</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>1477</c:v>
+                  <c:v>1488.5</c:v>
                 </c:pt>
                 <c:pt idx="72">
+                  <c:v>1497.5</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1491.9</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1488.4</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1500.7</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1495</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1504.7</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>1486.7</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1499.9</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1501.7</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1508</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1511.4</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1518.2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>1517</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1513.3</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1510.6</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>1511.4</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1509.8</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1501</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1479.2</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1474.7</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1483.5</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1482.7</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1472.7</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1475.5</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1479.2</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1460</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1472.8</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1480.8</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1480.3</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1479.2</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1476.8</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1473.6</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1473.2</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1488.5</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="106">
+                  <c:v>1477.5</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1478.4</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1449.4</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1456</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1462.3</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1472.7</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1490.9</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1489.3</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1493.4</c:v>
+                </c:pt>
+                <c:pt idx="115">
                   <c:v>1497.5</c:v>
                 </c:pt>
-                <c:pt idx="74">
-                  <c:v>1491.9</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>1488.4</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>1500.7</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>1495</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>1504.7</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>1486.7</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>1499.9</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1501.7</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>1508</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>1511.4</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>1518.2</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>1517</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>1513.3</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>1510.6</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>1511.4</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>1509.8</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>1501</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>1479.2</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>1474.7</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>1483.5</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>1482.7</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>1472.7</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>1475.5</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>1479.2</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>1460</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>1472.8</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>1480.8</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>1480.3</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>1479.2</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>1476.8</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>1473.6</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>1473.2</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>1488.5</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>1477.5</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>1478.4</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>1449.4</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>1456</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>1462.3</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>1472.7</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>1490.9</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1489.3</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1493.4</c:v>
-                </c:pt>
                 <c:pt idx="116">
-                  <c:v>1497.5</c:v>
+                  <c:v>1492.9</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>1492.9</c:v>
+                  <c:v>1508.7</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>1508.7</c:v>
+                  <c:v>1496.7</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>1508.7</c:v>
+                  <c:v>1496.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2616,10 +2616,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>1475.6</v>
+        <v>1477.1</v>
       </c>
       <c r="C2" s="3">
-        <v>1471.5</v>
+        <v>1476.5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2627,10 +2627,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>1477.1</v>
+        <v>1472.4</v>
       </c>
       <c r="C3" s="3">
-        <v>1476.5</v>
+        <v>1469.3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2638,10 +2638,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>1472.4</v>
+        <v>1465.6</v>
       </c>
       <c r="C4" s="3">
-        <v>1469.3</v>
+        <v>1468.3</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2649,10 +2649,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>1465.6</v>
+        <v>1464.9</v>
       </c>
       <c r="C5" s="3">
-        <v>1468.3</v>
+        <v>1462.7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2660,10 +2660,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>1464.9</v>
+        <v>1470.6</v>
       </c>
       <c r="C6" s="3">
-        <v>1462.7</v>
+        <v>1466.8</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2671,10 +2671,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1470.6</v>
+        <v>1469.9</v>
       </c>
       <c r="C7" s="3">
-        <v>1466.8</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2682,10 +2682,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>1469.9</v>
+        <v>1468.4</v>
       </c>
       <c r="C8" s="3">
-        <v>1468</v>
+        <v>1469.4</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2693,10 +2693,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="3">
-        <v>1468.4</v>
+        <v>1468</v>
       </c>
       <c r="C9" s="3">
-        <v>1469.4</v>
+        <v>1466.9</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2704,10 +2704,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>1468</v>
+        <v>1473.5</v>
       </c>
       <c r="C10" s="3">
-        <v>1466.9</v>
+        <v>1473.6</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2715,10 +2715,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="3">
-        <v>1473.5</v>
+        <v>1468.8</v>
       </c>
       <c r="C11" s="3">
-        <v>1473.6</v>
+        <v>1473.3</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2726,10 +2726,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="3">
-        <v>1468.8</v>
+        <v>1466.9</v>
       </c>
       <c r="C12" s="3">
-        <v>1473.3</v>
+        <v>1469.8</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2737,10 +2737,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3">
-        <v>1466.9</v>
+        <v>1472.3</v>
       </c>
       <c r="C13" s="3">
-        <v>1469.8</v>
+        <v>1469.9</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2748,10 +2748,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="3">
-        <v>1472.3</v>
+        <v>1470.4</v>
       </c>
       <c r="C14" s="3">
-        <v>1469.9</v>
+        <v>1470.8</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2759,10 +2759,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="3">
-        <v>1470.4</v>
+        <v>1473</v>
       </c>
       <c r="C15" s="3">
-        <v>1470.8</v>
+        <v>1471.9</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2770,10 +2770,10 @@
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>1473</v>
+        <v>1473.7</v>
       </c>
       <c r="C16" s="3">
-        <v>1471.9</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2781,10 +2781,10 @@
         <v>18</v>
       </c>
       <c r="B17" s="3">
-        <v>1473.7</v>
+        <v>1471</v>
       </c>
       <c r="C17" s="3">
-        <v>1477</v>
+        <v>1468.6</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2792,10 +2792,10 @@
         <v>19</v>
       </c>
       <c r="B18" s="3">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="C18" s="3">
-        <v>1468.6</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2803,10 +2803,10 @@
         <v>20</v>
       </c>
       <c r="B19" s="3">
-        <v>1477</v>
+        <v>1479.8</v>
       </c>
       <c r="C19" s="3">
-        <v>1473</v>
+        <v>1474.5</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2814,10 +2814,10 @@
         <v>21</v>
       </c>
       <c r="B20" s="3">
-        <v>1479.8</v>
+        <v>1478.3</v>
       </c>
       <c r="C20" s="3">
-        <v>1474.5</v>
+        <v>1473.1</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2825,10 +2825,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="3">
-        <v>1478.3</v>
+        <v>1476.3</v>
       </c>
       <c r="C21" s="3">
-        <v>1473.1</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2836,10 +2836,10 @@
         <v>23</v>
       </c>
       <c r="B22" s="3">
-        <v>1476.3</v>
+        <v>1480.1</v>
       </c>
       <c r="C22" s="3">
-        <v>1478</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2847,7 +2847,7 @@
         <v>24</v>
       </c>
       <c r="B23" s="3">
-        <v>1480.1</v>
+        <v>1483.6</v>
       </c>
       <c r="C23" s="3">
         <v>1481</v>
@@ -2858,10 +2858,10 @@
         <v>25</v>
       </c>
       <c r="B24" s="3">
-        <v>1483.6</v>
+        <v>1449.8</v>
       </c>
       <c r="C24" s="3">
-        <v>1481</v>
+        <v>1445.7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2869,10 +2869,10 @@
         <v>26</v>
       </c>
       <c r="B25" s="3">
-        <v>1449.8</v>
+        <v>1440.3</v>
       </c>
       <c r="C25" s="3">
-        <v>1445.7</v>
+        <v>1442.2</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2880,10 +2880,10 @@
         <v>27</v>
       </c>
       <c r="B26" s="3">
-        <v>1440.3</v>
+        <v>1429.8</v>
       </c>
       <c r="C26" s="3">
-        <v>1442.2</v>
+        <v>1434.1</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2891,10 +2891,10 @@
         <v>28</v>
       </c>
       <c r="B27" s="3">
-        <v>1429.8</v>
+        <v>1439</v>
       </c>
       <c r="C27" s="3">
-        <v>1434.1</v>
+        <v>1439.5</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2902,10 +2902,10 @@
         <v>29</v>
       </c>
       <c r="B28" s="3">
-        <v>1439</v>
+        <v>1441.8</v>
       </c>
       <c r="C28" s="3">
-        <v>1439.5</v>
+        <v>1444.7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2913,10 +2913,10 @@
         <v>30</v>
       </c>
       <c r="B29" s="3">
-        <v>1441.8</v>
+        <v>1443.8</v>
       </c>
       <c r="C29" s="3">
-        <v>1444.7</v>
+        <v>1445.6</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2924,10 +2924,10 @@
         <v>31</v>
       </c>
       <c r="B30" s="3">
-        <v>1443.8</v>
+        <v>1445.4</v>
       </c>
       <c r="C30" s="3">
-        <v>1445.6</v>
+        <v>1447.1</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2935,10 +2935,10 @@
         <v>32</v>
       </c>
       <c r="B31" s="3">
-        <v>1445.4</v>
+        <v>1445.8</v>
       </c>
       <c r="C31" s="3">
-        <v>1447.1</v>
+        <v>1447.6</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2946,10 +2946,10 @@
         <v>33</v>
       </c>
       <c r="B32" s="3">
-        <v>1445.8</v>
+        <v>1450.6</v>
       </c>
       <c r="C32" s="3">
-        <v>1447.6</v>
+        <v>1451.8</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2957,10 +2957,10 @@
         <v>34</v>
       </c>
       <c r="B33" s="3">
-        <v>1450.6</v>
+        <v>1457.6</v>
       </c>
       <c r="C33" s="3">
-        <v>1451.8</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2968,10 +2968,10 @@
         <v>35</v>
       </c>
       <c r="B34" s="3">
-        <v>1457.6</v>
+        <v>1468.4</v>
       </c>
       <c r="C34" s="3">
-        <v>1459</v>
+        <v>1468.8</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2979,10 +2979,10 @@
         <v>36</v>
       </c>
       <c r="B35" s="3">
-        <v>1468.4</v>
+        <v>1473.7</v>
       </c>
       <c r="C35" s="3">
-        <v>1468.8</v>
+        <v>1478.8</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2990,10 +2990,10 @@
         <v>37</v>
       </c>
       <c r="B36" s="3">
-        <v>1473.7</v>
+        <v>1477.5</v>
       </c>
       <c r="C36" s="3">
-        <v>1478.8</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -3001,10 +3001,10 @@
         <v>38</v>
       </c>
       <c r="B37" s="3">
-        <v>1477.5</v>
+        <v>1469.7</v>
       </c>
       <c r="C37" s="3">
-        <v>1464</v>
+        <v>1469.2</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -3012,10 +3012,10 @@
         <v>39</v>
       </c>
       <c r="B38" s="3">
-        <v>1469.7</v>
+        <v>1473.6</v>
       </c>
       <c r="C38" s="3">
-        <v>1469.2</v>
+        <v>1474.5</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -3023,10 +3023,10 @@
         <v>40</v>
       </c>
       <c r="B39" s="3">
-        <v>1473.6</v>
+        <v>1473.7</v>
       </c>
       <c r="C39" s="3">
-        <v>1474.5</v>
+        <v>1473.1</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -3034,10 +3034,10 @@
         <v>41</v>
       </c>
       <c r="B40" s="3">
-        <v>1473.7</v>
+        <v>1478.1</v>
       </c>
       <c r="C40" s="3">
-        <v>1473.1</v>
+        <v>1476.7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -3045,10 +3045,10 @@
         <v>42</v>
       </c>
       <c r="B41" s="3">
-        <v>1478.1</v>
+        <v>1471.3</v>
       </c>
       <c r="C41" s="3">
-        <v>1476.7</v>
+        <v>1465.9</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -3056,10 +3056,10 @@
         <v>43</v>
       </c>
       <c r="B42" s="3">
-        <v>1471.3</v>
+        <v>1469.9</v>
       </c>
       <c r="C42" s="3">
-        <v>1465.9</v>
+        <v>1464.5</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3067,10 +3067,10 @@
         <v>44</v>
       </c>
       <c r="B43" s="3">
-        <v>1469.9</v>
+        <v>1465.8</v>
       </c>
       <c r="C43" s="3">
-        <v>1464.5</v>
+        <v>1462.5</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -3078,10 +3078,10 @@
         <v>45</v>
       </c>
       <c r="B44" s="3">
-        <v>1465.8</v>
+        <v>1440.6</v>
       </c>
       <c r="C44" s="3">
-        <v>1462.5</v>
+        <v>1443.9</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -3089,10 +3089,10 @@
         <v>46</v>
       </c>
       <c r="B45" s="3">
-        <v>1440.6</v>
+        <v>1446.2</v>
       </c>
       <c r="C45" s="3">
-        <v>1443.9</v>
+        <v>1437.5</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -3100,10 +3100,10 @@
         <v>47</v>
       </c>
       <c r="B46" s="3">
-        <v>1446.2</v>
+        <v>1422.5</v>
       </c>
       <c r="C46" s="3">
-        <v>1437.5</v>
+        <v>1436.1</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -3111,10 +3111,10 @@
         <v>48</v>
       </c>
       <c r="B47" s="3">
-        <v>1422.5</v>
+        <v>1426.3</v>
       </c>
       <c r="C47" s="3">
-        <v>1436.1</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -3122,10 +3122,10 @@
         <v>49</v>
       </c>
       <c r="B48" s="3">
-        <v>1426.3</v>
+        <v>1439.5</v>
       </c>
       <c r="C48" s="3">
-        <v>1434</v>
+        <v>1443.5</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -3133,10 +3133,10 @@
         <v>50</v>
       </c>
       <c r="B49" s="3">
-        <v>1439.5</v>
+        <v>1464.3</v>
       </c>
       <c r="C49" s="3">
-        <v>1443.5</v>
+        <v>1451.5</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -3144,10 +3144,10 @@
         <v>51</v>
       </c>
       <c r="B50" s="3">
-        <v>1464.3</v>
+        <v>1445.4</v>
       </c>
       <c r="C50" s="3">
-        <v>1451.5</v>
+        <v>1446.6</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -3155,10 +3155,10 @@
         <v>52</v>
       </c>
       <c r="B51" s="3">
-        <v>1445.4</v>
+        <v>1450.2</v>
       </c>
       <c r="C51" s="3">
-        <v>1446.6</v>
+        <v>1459.5</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -3166,10 +3166,10 @@
         <v>53</v>
       </c>
       <c r="B52" s="3">
-        <v>1450.2</v>
+        <v>1469</v>
       </c>
       <c r="C52" s="3">
-        <v>1459.5</v>
+        <v>1463.7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -3177,10 +3177,10 @@
         <v>54</v>
       </c>
       <c r="B53" s="3">
-        <v>1469</v>
+        <v>1469.5</v>
       </c>
       <c r="C53" s="3">
-        <v>1463.7</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -3188,10 +3188,10 @@
         <v>55</v>
       </c>
       <c r="B54" s="3">
-        <v>1469.5</v>
+        <v>1460.3</v>
       </c>
       <c r="C54" s="3">
-        <v>1463</v>
+        <v>1457.7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -3199,10 +3199,10 @@
         <v>56</v>
       </c>
       <c r="B55" s="3">
-        <v>1460.3</v>
+        <v>1459.1</v>
       </c>
       <c r="C55" s="3">
-        <v>1457.7</v>
+        <v>1457.2</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -3210,10 +3210,10 @@
         <v>57</v>
       </c>
       <c r="B56" s="3">
-        <v>1459.1</v>
+        <v>1450.1</v>
       </c>
       <c r="C56" s="3">
-        <v>1457.2</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -3221,10 +3221,10 @@
         <v>58</v>
       </c>
       <c r="B57" s="3">
-        <v>1450.1</v>
+        <v>1440.2</v>
       </c>
       <c r="C57" s="3">
-        <v>1447</v>
+        <v>1438.6</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -3232,10 +3232,10 @@
         <v>59</v>
       </c>
       <c r="B58" s="3">
-        <v>1440.2</v>
+        <v>1444.9</v>
       </c>
       <c r="C58" s="3">
-        <v>1438.6</v>
+        <v>1444.6</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -3243,10 +3243,10 @@
         <v>60</v>
       </c>
       <c r="B59" s="3">
-        <v>1444.9</v>
+        <v>1445.5</v>
       </c>
       <c r="C59" s="3">
-        <v>1444.6</v>
+        <v>1448.9</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -3254,10 +3254,10 @@
         <v>61</v>
       </c>
       <c r="B60" s="3">
-        <v>1445.5</v>
+        <v>1446.6</v>
       </c>
       <c r="C60" s="3">
-        <v>1448.9</v>
+        <v>1446.6</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -3265,10 +3265,10 @@
         <v>62</v>
       </c>
       <c r="B61" s="3">
-        <v>1446.6</v>
+        <v>1440</v>
       </c>
       <c r="C61" s="3">
-        <v>1446.6</v>
+        <v>1442.9</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -3276,10 +3276,10 @@
         <v>63</v>
       </c>
       <c r="B62" s="3">
-        <v>1440</v>
+        <v>1442.5</v>
       </c>
       <c r="C62" s="3">
-        <v>1442.9</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -3287,10 +3287,10 @@
         <v>64</v>
       </c>
       <c r="B63" s="3">
-        <v>1442.5</v>
+        <v>1429.4</v>
       </c>
       <c r="C63" s="3">
-        <v>1441</v>
+        <v>1427.8</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -3298,10 +3298,10 @@
         <v>65</v>
       </c>
       <c r="B64" s="3">
-        <v>1429.4</v>
+        <v>1425.8</v>
       </c>
       <c r="C64" s="3">
-        <v>1427.8</v>
+        <v>1433.5</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -3309,10 +3309,10 @@
         <v>66</v>
       </c>
       <c r="B65" s="3">
-        <v>1425.8</v>
+        <v>1439.7</v>
       </c>
       <c r="C65" s="3">
-        <v>1433.5</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -3320,10 +3320,10 @@
         <v>67</v>
       </c>
       <c r="B66" s="3">
-        <v>1439.7</v>
+        <v>1466.1</v>
       </c>
       <c r="C66" s="3">
-        <v>1440</v>
+        <v>1485.7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -3331,10 +3331,10 @@
         <v>68</v>
       </c>
       <c r="B67" s="3">
-        <v>1466.1</v>
+        <v>1476.2</v>
       </c>
       <c r="C67" s="3">
-        <v>1485.7</v>
+        <v>1462.9</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -3342,10 +3342,10 @@
         <v>69</v>
       </c>
       <c r="B68" s="3">
-        <v>1476.2</v>
+        <v>1468.1</v>
       </c>
       <c r="C68" s="3">
-        <v>1462.9</v>
+        <v>1482.2</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -3353,10 +3353,10 @@
         <v>70</v>
       </c>
       <c r="B69" s="3">
-        <v>1468.1</v>
+        <v>1476.4</v>
       </c>
       <c r="C69" s="3">
-        <v>1482.2</v>
+        <v>1481.6</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -3364,10 +3364,10 @@
         <v>71</v>
       </c>
       <c r="B70" s="3">
-        <v>1476.4</v>
+        <v>1495.5</v>
       </c>
       <c r="C70" s="3">
-        <v>1481.6</v>
+        <v>1473.7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -3375,10 +3375,10 @@
         <v>72</v>
       </c>
       <c r="B71" s="3">
-        <v>1495.5</v>
+        <v>1469.2</v>
       </c>
       <c r="C71" s="3">
-        <v>1473.7</v>
+        <v>1465.7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -3386,10 +3386,10 @@
         <v>73</v>
       </c>
       <c r="B72" s="3">
-        <v>1469.2</v>
+        <v>1466.5</v>
       </c>
       <c r="C72" s="3">
-        <v>1465.7</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -3397,10 +3397,10 @@
         <v>74</v>
       </c>
       <c r="B73" s="3">
-        <v>1466.5</v>
+        <v>1481.2</v>
       </c>
       <c r="C73" s="3">
-        <v>1477</v>
+        <v>1488.5</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -3408,10 +3408,10 @@
         <v>75</v>
       </c>
       <c r="B74" s="3">
-        <v>1481.2</v>
+        <v>1493.7</v>
       </c>
       <c r="C74" s="3">
-        <v>1488.5</v>
+        <v>1497.5</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -3419,10 +3419,10 @@
         <v>76</v>
       </c>
       <c r="B75" s="3">
-        <v>1493.7</v>
+        <v>1497.5</v>
       </c>
       <c r="C75" s="3">
-        <v>1497.5</v>
+        <v>1491.9</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -3430,10 +3430,10 @@
         <v>77</v>
       </c>
       <c r="B76" s="3">
-        <v>1497.5</v>
+        <v>1493.6</v>
       </c>
       <c r="C76" s="3">
-        <v>1491.9</v>
+        <v>1488.4</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -3441,10 +3441,10 @@
         <v>78</v>
       </c>
       <c r="B77" s="3">
-        <v>1493.6</v>
+        <v>1483.1</v>
       </c>
       <c r="C77" s="3">
-        <v>1488.4</v>
+        <v>1500.7</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -3452,10 +3452,10 @@
         <v>79</v>
       </c>
       <c r="B78" s="3">
-        <v>1483.1</v>
+        <v>1501</v>
       </c>
       <c r="C78" s="3">
-        <v>1500.7</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -3463,10 +3463,10 @@
         <v>80</v>
       </c>
       <c r="B79" s="3">
-        <v>1501</v>
+        <v>1500.6</v>
       </c>
       <c r="C79" s="3">
-        <v>1495</v>
+        <v>1504.7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -3474,10 +3474,10 @@
         <v>81</v>
       </c>
       <c r="B80" s="3">
-        <v>1500.6</v>
+        <v>1517.3</v>
       </c>
       <c r="C80" s="3">
-        <v>1504.7</v>
+        <v>1486.7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -3485,10 +3485,10 @@
         <v>82</v>
       </c>
       <c r="B81" s="3">
-        <v>1517.3</v>
+        <v>1495.2</v>
       </c>
       <c r="C81" s="3">
-        <v>1486.7</v>
+        <v>1499.9</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -3496,10 +3496,10 @@
         <v>83</v>
       </c>
       <c r="B82" s="3">
-        <v>1495.2</v>
+        <v>1499.7</v>
       </c>
       <c r="C82" s="3">
-        <v>1499.9</v>
+        <v>1501.7</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -3507,10 +3507,10 @@
         <v>84</v>
       </c>
       <c r="B83" s="3">
-        <v>1499.7</v>
+        <v>1507</v>
       </c>
       <c r="C83" s="3">
-        <v>1501.7</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -3518,10 +3518,10 @@
         <v>85</v>
       </c>
       <c r="B84" s="3">
-        <v>1507</v>
+        <v>1508.9</v>
       </c>
       <c r="C84" s="3">
-        <v>1508</v>
+        <v>1511.4</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -3529,10 +3529,10 @@
         <v>86</v>
       </c>
       <c r="B85" s="3">
-        <v>1508.9</v>
+        <v>1515.7</v>
       </c>
       <c r="C85" s="3">
-        <v>1511.4</v>
+        <v>1518.2</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -3540,10 +3540,10 @@
         <v>87</v>
       </c>
       <c r="B86" s="3">
-        <v>1515.7</v>
+        <v>1530.1</v>
       </c>
       <c r="C86" s="3">
-        <v>1518.2</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -3551,10 +3551,10 @@
         <v>88</v>
       </c>
       <c r="B87" s="3">
-        <v>1530.1</v>
+        <v>1501.3</v>
       </c>
       <c r="C87" s="3">
-        <v>1517</v>
+        <v>1513.3</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -3562,10 +3562,10 @@
         <v>89</v>
       </c>
       <c r="B88" s="3">
-        <v>1501.3</v>
+        <v>1519.7</v>
       </c>
       <c r="C88" s="3">
-        <v>1513.3</v>
+        <v>1510.6</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -3573,10 +3573,10 @@
         <v>90</v>
       </c>
       <c r="B89" s="3">
-        <v>1519.7</v>
+        <v>1505.2</v>
       </c>
       <c r="C89" s="3">
-        <v>1510.6</v>
+        <v>1511.4</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -3584,10 +3584,10 @@
         <v>91</v>
       </c>
       <c r="B90" s="3">
-        <v>1505.2</v>
+        <v>1506.3</v>
       </c>
       <c r="C90" s="3">
-        <v>1511.4</v>
+        <v>1509.8</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -3595,10 +3595,10 @@
         <v>92</v>
       </c>
       <c r="B91" s="3">
-        <v>1506.3</v>
+        <v>1504.2</v>
       </c>
       <c r="C91" s="3">
-        <v>1509.8</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -3606,10 +3606,10 @@
         <v>93</v>
       </c>
       <c r="B92" s="3">
-        <v>1504.2</v>
+        <v>1470.6</v>
       </c>
       <c r="C92" s="3">
-        <v>1501</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -3617,10 +3617,10 @@
         <v>94</v>
       </c>
       <c r="B93" s="3">
-        <v>1470.6</v>
+        <v>1482.5</v>
       </c>
       <c r="C93" s="3">
-        <v>1479.2</v>
+        <v>1474.7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -3631,7 +3631,7 @@
         <v>1482.5</v>
       </c>
       <c r="C94" s="3">
-        <v>1474.7</v>
+        <v>1483.5</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -3639,10 +3639,10 @@
         <v>96</v>
       </c>
       <c r="B95" s="3">
-        <v>1482.5</v>
+        <v>1489.3</v>
       </c>
       <c r="C95" s="3">
-        <v>1483.5</v>
+        <v>1482.7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -3650,10 +3650,10 @@
         <v>97</v>
       </c>
       <c r="B96" s="3">
-        <v>1489.3</v>
+        <v>1481.2</v>
       </c>
       <c r="C96" s="3">
-        <v>1482.7</v>
+        <v>1472.7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -3661,10 +3661,10 @@
         <v>98</v>
       </c>
       <c r="B97" s="3">
-        <v>1481.2</v>
+        <v>1474.2</v>
       </c>
       <c r="C97" s="3">
-        <v>1472.7</v>
+        <v>1475.5</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -3672,10 +3672,10 @@
         <v>99</v>
       </c>
       <c r="B98" s="3">
-        <v>1474.2</v>
+        <v>1474.6</v>
       </c>
       <c r="C98" s="3">
-        <v>1475.5</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -3683,10 +3683,10 @@
         <v>100</v>
       </c>
       <c r="B99" s="3">
-        <v>1474.6</v>
+        <v>1483.5</v>
       </c>
       <c r="C99" s="3">
-        <v>1479.2</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -3694,10 +3694,10 @@
         <v>101</v>
       </c>
       <c r="B100" s="3">
-        <v>1483.5</v>
+        <v>1477.2</v>
       </c>
       <c r="C100" s="3">
-        <v>1460</v>
+        <v>1472.8</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -3705,10 +3705,10 @@
         <v>102</v>
       </c>
       <c r="B101" s="3">
-        <v>1477.2</v>
+        <v>1468.5</v>
       </c>
       <c r="C101" s="3">
-        <v>1472.8</v>
+        <v>1480.8</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -3716,10 +3716,10 @@
         <v>103</v>
       </c>
       <c r="B102" s="3">
-        <v>1468.5</v>
+        <v>1476</v>
       </c>
       <c r="C102" s="3">
-        <v>1480.8</v>
+        <v>1480.3</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -3727,10 +3727,10 @@
         <v>104</v>
       </c>
       <c r="B103" s="3">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="C103" s="3">
-        <v>1480.3</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -3738,10 +3738,10 @@
         <v>105</v>
       </c>
       <c r="B104" s="3">
-        <v>1481</v>
+        <v>1484.5</v>
       </c>
       <c r="C104" s="3">
-        <v>1479.2</v>
+        <v>1476.8</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -3749,10 +3749,10 @@
         <v>106</v>
       </c>
       <c r="B105" s="3">
-        <v>1484.5</v>
+        <v>1472.5</v>
       </c>
       <c r="C105" s="3">
-        <v>1476.8</v>
+        <v>1473.6</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -3760,10 +3760,10 @@
         <v>107</v>
       </c>
       <c r="B106" s="3">
-        <v>1472.5</v>
+        <v>1473.6</v>
       </c>
       <c r="C106" s="3">
-        <v>1473.6</v>
+        <v>1473.2</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -3771,10 +3771,10 @@
         <v>108</v>
       </c>
       <c r="B107" s="3">
-        <v>1473.6</v>
+        <v>1479</v>
       </c>
       <c r="C107" s="3">
-        <v>1473.2</v>
+        <v>1488.5</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -3782,10 +3782,10 @@
         <v>109</v>
       </c>
       <c r="B108" s="3">
-        <v>1479</v>
+        <v>1483.3</v>
       </c>
       <c r="C108" s="3">
-        <v>1488.5</v>
+        <v>1477.5</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -3793,10 +3793,10 @@
         <v>110</v>
       </c>
       <c r="B109" s="3">
-        <v>1483.3</v>
+        <v>1462.8</v>
       </c>
       <c r="C109" s="3">
-        <v>1477.5</v>
+        <v>1478.4</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -3804,10 +3804,10 @@
         <v>111</v>
       </c>
       <c r="B110" s="3">
-        <v>1462.8</v>
+        <v>1455.1</v>
       </c>
       <c r="C110" s="3">
-        <v>1478.4</v>
+        <v>1449.4</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -3815,10 +3815,10 @@
         <v>112</v>
       </c>
       <c r="B111" s="3">
-        <v>1455.1</v>
+        <v>1454</v>
       </c>
       <c r="C111" s="3">
-        <v>1449.4</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -3826,10 +3826,10 @@
         <v>113</v>
       </c>
       <c r="B112" s="3">
-        <v>1454</v>
+        <v>1471.7</v>
       </c>
       <c r="C112" s="3">
-        <v>1456</v>
+        <v>1462.3</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -3837,10 +3837,10 @@
         <v>114</v>
       </c>
       <c r="B113" s="3">
-        <v>1471.7</v>
+        <v>1472.4</v>
       </c>
       <c r="C113" s="3">
-        <v>1462.3</v>
+        <v>1472.7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -3848,10 +3848,10 @@
         <v>115</v>
       </c>
       <c r="B114" s="3">
-        <v>1472.4</v>
+        <v>1489.9</v>
       </c>
       <c r="C114" s="3">
-        <v>1472.7</v>
+        <v>1490.9</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -3859,10 +3859,10 @@
         <v>116</v>
       </c>
       <c r="B115" s="3">
-        <v>1489.9</v>
+        <v>1490.6</v>
       </c>
       <c r="C115" s="3">
-        <v>1490.9</v>
+        <v>1489.3</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -3870,10 +3870,10 @@
         <v>117</v>
       </c>
       <c r="B116" s="3">
-        <v>1490.6</v>
+        <v>1491</v>
       </c>
       <c r="C116" s="3">
-        <v>1489.3</v>
+        <v>1493.4</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -3881,10 +3881,10 @@
         <v>118</v>
       </c>
       <c r="B117" s="3">
-        <v>1491</v>
+        <v>1500.8</v>
       </c>
       <c r="C117" s="3">
-        <v>1493.4</v>
+        <v>1497.5</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -3892,10 +3892,10 @@
         <v>119</v>
       </c>
       <c r="B118" s="3">
-        <v>1500.8</v>
+        <v>1500.3</v>
       </c>
       <c r="C118" s="3">
-        <v>1497.5</v>
+        <v>1492.9</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -3903,10 +3903,10 @@
         <v>120</v>
       </c>
       <c r="B119" s="3">
-        <v>1500.3</v>
+        <v>1507.8</v>
       </c>
       <c r="C119" s="3">
-        <v>1492.9</v>
+        <v>1508.7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -3914,10 +3914,10 @@
         <v>121</v>
       </c>
       <c r="B120" s="3">
-        <v>1507.8</v>
+        <v>1506.8</v>
       </c>
       <c r="C120" s="3">
-        <v>1508.7</v>
+        <v>1496.7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -3925,10 +3925,10 @@
         <v>122</v>
       </c>
       <c r="B121" s="3">
-        <v>1506.8</v>
+        <v>1506.1</v>
       </c>
       <c r="C121" s="4">
-        <v>1508.7</v>
+        <v>1496.7</v>
       </c>
     </row>
   </sheetData>
